--- a/excel/Synthetic_Prediction_SM_IN.xlsx
+++ b/excel/Synthetic_Prediction_SM_IN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DE\sem 5\Codes\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F66D8D1-FF03-4FA7-A8BE-C4876A43EFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C8AAFC-2C46-4F99-AD3A-6A3B6531CA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-756" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38366,13 +38366,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N702" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O702" s="5">
         <v>0</v>
       </c>
       <c r="P702" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q702" s="6">
         <v>177.9919202713117</v>
@@ -38420,13 +38420,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N703" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O703" s="5">
         <v>0</v>
       </c>
       <c r="P703" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q703" s="6">
         <v>216.49799608682349</v>
@@ -38474,13 +38474,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N704" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O704" s="5">
         <v>0</v>
       </c>
       <c r="P704" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q704" s="6">
         <v>249.51785520798541</v>
@@ -38528,13 +38528,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N705" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O705" s="5">
         <v>0</v>
       </c>
       <c r="P705" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q705" s="6">
         <v>192.0850436767127</v>
@@ -38582,13 +38582,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N706" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O706" s="5">
         <v>0</v>
       </c>
       <c r="P706" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q706" s="6">
         <v>147.4814866026166</v>
@@ -38636,13 +38636,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N707" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O707" s="5">
         <v>0</v>
       </c>
       <c r="P707" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q707" s="6">
         <v>255.2593411255647</v>
@@ -38690,13 +38690,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N708" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O708" s="5">
         <v>0</v>
       </c>
       <c r="P708" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q708" s="6">
         <v>90.390832603644355</v>
@@ -38744,13 +38744,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N709" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O709" s="5">
         <v>0</v>
       </c>
       <c r="P709" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q709" s="6">
         <v>76.400597609747109</v>
@@ -38798,13 +38798,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N710" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O710" s="5">
         <v>0</v>
       </c>
       <c r="P710" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q710" s="6">
         <v>101.6090823197472</v>
@@ -38852,13 +38852,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N711" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O711" s="5">
         <v>0</v>
       </c>
       <c r="P711" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q711" s="6">
         <v>190.58539804431641</v>
@@ -38906,13 +38906,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N712" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O712" s="5">
         <v>0</v>
       </c>
       <c r="P712" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q712" s="6">
         <v>240.53174598064831</v>
@@ -38960,13 +38960,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N713" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O713" s="5">
         <v>0</v>
       </c>
       <c r="P713" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q713" s="6">
         <v>107.98461264267461</v>
@@ -39014,13 +39014,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N714" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O714" s="5">
         <v>0</v>
       </c>
       <c r="P714" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q714" s="6">
         <v>212.10673446363421</v>
@@ -39068,13 +39068,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N715" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O715" s="5">
         <v>0</v>
       </c>
       <c r="P715" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q715" s="6">
         <v>263.5298210107847</v>
@@ -39122,13 +39122,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N716" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O716" s="5">
         <v>0</v>
       </c>
       <c r="P716" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q716" s="6">
         <v>122.887809759578</v>
@@ -39176,13 +39176,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N717" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O717" s="5">
         <v>0</v>
       </c>
       <c r="P717" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q717" s="6">
         <v>224.88553512694739</v>
@@ -39230,13 +39230,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N718" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O718" s="5">
         <v>0</v>
       </c>
       <c r="P718" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q718" s="6">
         <v>170.46274558792939</v>
@@ -39284,13 +39284,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N719" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O719" s="5">
         <v>0</v>
       </c>
       <c r="P719" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q719" s="6">
         <v>185.38071324740869</v>
@@ -39338,13 +39338,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N720" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O720" s="5">
         <v>0</v>
       </c>
       <c r="P720" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q720" s="6">
         <v>247.58801201690349</v>
@@ -39392,13 +39392,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N721" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O721" s="5">
         <v>0</v>
       </c>
       <c r="P721" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q721" s="6">
         <v>142.42804586901329</v>
@@ -39446,13 +39446,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N722" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O722" s="5">
         <v>0</v>
       </c>
       <c r="P722" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q722" s="6">
         <v>82.430855028200398</v>
@@ -39500,13 +39500,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N723" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O723" s="5">
         <v>0</v>
       </c>
       <c r="P723" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q723" s="6">
         <v>252.51323540655841</v>
@@ -39554,13 +39554,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N724" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O724" s="5">
         <v>0</v>
       </c>
       <c r="P724" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q724" s="6">
         <v>179.591619791715</v>
@@ -39608,13 +39608,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N725" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O725" s="5">
         <v>0</v>
       </c>
       <c r="P725" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q725" s="6">
         <v>149.87340677250319</v>
@@ -39662,13 +39662,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N726" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O726" s="5">
         <v>0</v>
       </c>
       <c r="P726" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q726" s="6">
         <v>237.72851994604699</v>
@@ -39716,13 +39716,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N727" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O727" s="5">
         <v>0</v>
       </c>
       <c r="P727" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q727" s="6">
         <v>103.4681106078348</v>
@@ -39770,13 +39770,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N728" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O728" s="5">
         <v>0</v>
       </c>
       <c r="P728" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q728" s="6">
         <v>168.64621363365569</v>
@@ -39824,13 +39824,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N729" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O729" s="5">
         <v>0</v>
       </c>
       <c r="P729" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q729" s="6">
         <v>163.51391749156241</v>
@@ -39878,13 +39878,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N730" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O730" s="5">
         <v>0</v>
       </c>
       <c r="P730" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q730" s="6">
         <v>229.01384233192351</v>
@@ -39932,13 +39932,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N731" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O731" s="5">
         <v>0</v>
       </c>
       <c r="P731" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q731" s="6">
         <v>156.26631011523719</v>
@@ -39986,13 +39986,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N732" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O732" s="5">
         <v>0</v>
       </c>
       <c r="P732" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q732" s="6">
         <v>199.95671321431561</v>
@@ -40040,13 +40040,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N733" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O733" s="5">
         <v>0</v>
       </c>
       <c r="P733" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q733" s="6">
         <v>245.31792801947199</v>
@@ -40094,13 +40094,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N734" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O734" s="5">
         <v>0</v>
       </c>
       <c r="P734" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q734" s="6">
         <v>260.53644867029539</v>
@@ -40148,13 +40148,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N735" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O735" s="5">
         <v>0</v>
       </c>
       <c r="P735" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q735" s="6">
         <v>158.88034984604161</v>
@@ -40202,13 +40202,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N736" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O736" s="5">
         <v>0</v>
       </c>
       <c r="P736" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q736" s="6">
         <v>140.75937347501841</v>
@@ -40256,13 +40256,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N737" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O737" s="5">
         <v>0</v>
       </c>
       <c r="P737" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q737" s="6">
         <v>207.03712425473179</v>
@@ -40310,13 +40310,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N738" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O738" s="5">
         <v>0</v>
       </c>
       <c r="P738" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q738" s="6">
         <v>131.47819041621551</v>
@@ -40364,13 +40364,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N739" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O739" s="5">
         <v>0</v>
       </c>
       <c r="P739" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q739" s="6">
         <v>210.4501139271226</v>
@@ -40418,13 +40418,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N740" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O740" s="5">
         <v>0</v>
       </c>
       <c r="P740" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q740" s="6">
         <v>155.1832045773252</v>
@@ -40472,13 +40472,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N741" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O741" s="5">
         <v>0</v>
       </c>
       <c r="P741" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q741" s="6">
         <v>243.91927931917519</v>
@@ -40526,13 +40526,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N742" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O742" s="5">
         <v>0</v>
       </c>
       <c r="P742" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q742" s="6">
         <v>176.67115647715411</v>
@@ -40580,13 +40580,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N743" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O743" s="5">
         <v>0</v>
       </c>
       <c r="P743" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q743" s="6">
         <v>126.09561289832391</v>
@@ -40634,13 +40634,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N744" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O744" s="5">
         <v>0</v>
       </c>
       <c r="P744" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q744" s="6">
         <v>148.26596831567761</v>
@@ -40688,13 +40688,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N745" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O745" s="5">
         <v>0</v>
       </c>
       <c r="P745" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q745" s="6">
         <v>230.69054339179141</v>
@@ -40742,13 +40742,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N746" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O746" s="5">
         <v>0</v>
       </c>
       <c r="P746" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q746" s="6">
         <v>219.6975994371102</v>
@@ -40796,13 +40796,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N747" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O747" s="5">
         <v>0</v>
       </c>
       <c r="P747" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q747" s="6">
         <v>84.329411795820548</v>
@@ -40850,13 +40850,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N748" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O748" s="5">
         <v>0</v>
       </c>
       <c r="P748" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q748" s="6">
         <v>262.40517972221193</v>
@@ -40904,13 +40904,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N749" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O749" s="5">
         <v>0</v>
       </c>
       <c r="P749" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q749" s="6">
         <v>73.408818373262278</v>
@@ -40958,13 +40958,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N750" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O750" s="5">
         <v>0</v>
       </c>
       <c r="P750" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q750" s="6">
         <v>257.83462121714632</v>
@@ -41012,13 +41012,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N751" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O751" s="5">
         <v>0</v>
       </c>
       <c r="P751" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q751" s="6">
         <v>165.31434818633261</v>
@@ -41066,13 +41066,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N752" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O752" s="5">
         <v>0</v>
       </c>
       <c r="P752" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q752" s="6">
         <v>173.16060283604679</v>
@@ -41120,13 +41120,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N753" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O753" s="5">
         <v>0</v>
       </c>
       <c r="P753" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q753" s="6">
         <v>227.31493603745531</v>
@@ -41174,13 +41174,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N754" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O754" s="5">
         <v>0</v>
       </c>
       <c r="P754" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q754" s="6">
         <v>118.2206766639556</v>
@@ -41228,13 +41228,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N755" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O755" s="5">
         <v>0</v>
       </c>
       <c r="P755" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q755" s="6">
         <v>198.12434377767011</v>
@@ -41282,13 +41282,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N756" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O756" s="5">
         <v>0</v>
       </c>
       <c r="P756" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q756" s="6">
         <v>241.8573626466669</v>
@@ -41336,13 +41336,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N757" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O757" s="5">
         <v>0</v>
       </c>
       <c r="P757" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q757" s="6">
         <v>94.334847982586211</v>
@@ -41390,13 +41390,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N758" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O758" s="5">
         <v>0</v>
       </c>
       <c r="P758" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q758" s="6">
         <v>186.5853829540861</v>
@@ -41444,13 +41444,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N759" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O759" s="5">
         <v>0</v>
       </c>
       <c r="P759" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q759" s="6">
         <v>266.02722010275721</v>
@@ -41498,13 +41498,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N760" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O760" s="5">
         <v>0</v>
       </c>
       <c r="P760" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q760" s="6">
         <v>105.56884253505051</v>
@@ -41552,13 +41552,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N761" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O761" s="5">
         <v>0</v>
       </c>
       <c r="P761" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q761" s="6">
         <v>115.5767314665851</v>
@@ -41606,13 +41606,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N762" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O762" s="5">
         <v>0</v>
       </c>
       <c r="P762" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q762" s="6">
         <v>144.3463944107931</v>
@@ -41660,13 +41660,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N763" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O763" s="5">
         <v>0</v>
       </c>
       <c r="P763" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q763" s="6">
         <v>194.52718105722869</v>
@@ -41714,13 +41714,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N764" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O764" s="5">
         <v>0</v>
       </c>
       <c r="P764" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q764" s="6">
         <v>138.5773109371608</v>
@@ -41768,13 +41768,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N765" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O765" s="5">
         <v>0</v>
       </c>
       <c r="P765" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q765" s="6">
         <v>195.93338374197191</v>
@@ -41822,13 +41822,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N766" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O766" s="5">
         <v>0</v>
       </c>
       <c r="P766" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q766" s="6">
         <v>98.608658143134178</v>
@@ -41876,13 +41876,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N767" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O767" s="5">
         <v>0</v>
       </c>
       <c r="P767" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q767" s="6">
         <v>254.10833162883591</v>
@@ -41930,13 +41930,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N768" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O768" s="5">
         <v>0</v>
       </c>
       <c r="P768" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q768" s="6">
         <v>110.708123066396</v>
@@ -41984,13 +41984,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N769" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O769" s="5">
         <v>0</v>
       </c>
       <c r="P769" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q769" s="6">
         <v>133.12312395480191</v>
@@ -42038,13 +42038,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N770" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O770" s="5">
         <v>0</v>
       </c>
       <c r="P770" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q770" s="6">
         <v>235.23427955408999</v>
@@ -42092,13 +42092,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N771" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O771" s="5">
         <v>0</v>
       </c>
       <c r="P771" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q771" s="6">
         <v>136.84174384897199</v>
@@ -42146,13 +42146,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N772" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O772" s="5">
         <v>0</v>
       </c>
       <c r="P772" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q772" s="6">
         <v>87.496276741352958</v>
@@ -42200,13 +42200,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N773" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O773" s="5">
         <v>0</v>
       </c>
       <c r="P773" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q773" s="6">
         <v>160.7960489274742</v>
@@ -42254,13 +42254,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N774" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O774" s="5">
         <v>0</v>
       </c>
       <c r="P774" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q774" s="6">
         <v>106.1392000172837</v>
@@ -42308,13 +42308,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N775" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O775" s="5">
         <v>0</v>
       </c>
       <c r="P775" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q775" s="6">
         <v>121.3134676621403</v>
@@ -42362,13 +42362,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N776" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O776" s="5">
         <v>0</v>
       </c>
       <c r="P776" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q776" s="6">
         <v>93.782056079518114</v>
@@ -42416,13 +42416,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N777" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O777" s="5">
         <v>0</v>
       </c>
       <c r="P777" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q777" s="6">
         <v>129.18503706780211</v>
@@ -42470,13 +42470,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N778" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O778" s="5">
         <v>0</v>
       </c>
       <c r="P778" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q778" s="6">
         <v>218.77884645045441</v>
@@ -42524,13 +42524,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N779" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O779" s="5">
         <v>0</v>
       </c>
       <c r="P779" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q779" s="6">
         <v>222.02835436028181</v>
@@ -42578,13 +42578,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N780" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O780" s="5">
         <v>0</v>
       </c>
       <c r="P780" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q780" s="6">
         <v>202.3220940258654</v>
@@ -42632,13 +42632,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N781" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O781" s="5">
         <v>0</v>
       </c>
       <c r="P781" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q781" s="6">
         <v>88.353994820379469</v>
@@ -42686,13 +42686,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N782" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O782" s="5">
         <v>0</v>
       </c>
       <c r="P782" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q782" s="6">
         <v>112.4903161504798</v>
@@ -42740,13 +42740,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N783" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O783" s="5">
         <v>0</v>
       </c>
       <c r="P783" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q783" s="6">
         <v>188.68150891666471</v>
@@ -42794,13 +42794,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N784" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O784" s="5">
         <v>0</v>
       </c>
       <c r="P784" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q784" s="6">
         <v>116.17520068905419</v>
@@ -42848,13 +42848,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N785" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O785" s="5">
         <v>0</v>
       </c>
       <c r="P785" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q785" s="6">
         <v>153.31105490908021</v>
@@ -42902,13 +42902,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N786" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O786" s="5">
         <v>0</v>
       </c>
       <c r="P786" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q786" s="6">
         <v>233.2589083906561</v>
@@ -42956,13 +42956,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N787" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O787" s="5">
         <v>0</v>
       </c>
       <c r="P787" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q787" s="6">
         <v>79.778237933600039</v>
@@ -43010,13 +43010,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N788" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O788" s="5">
         <v>0</v>
       </c>
       <c r="P788" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q788" s="6">
         <v>166.14559241249219</v>
@@ -43064,13 +43064,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N789" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O789" s="5">
         <v>0</v>
       </c>
       <c r="P789" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q789" s="6">
         <v>204.50311027586079</v>
@@ -43118,13 +43118,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N790" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O790" s="5">
         <v>0</v>
       </c>
       <c r="P790" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q790" s="6">
         <v>268.83021501037678</v>
@@ -43172,13 +43172,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N791" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O791" s="5">
         <v>0</v>
       </c>
       <c r="P791" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q791" s="6">
         <v>236.28932996585931</v>
@@ -43226,13 +43226,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N792" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O792" s="5">
         <v>0</v>
       </c>
       <c r="P792" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q792" s="6">
         <v>215.0771830303085</v>
@@ -43280,13 +43280,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N793" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O793" s="5">
         <v>0</v>
       </c>
       <c r="P793" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q793" s="6">
         <v>80.562351694179469</v>
@@ -43334,13 +43334,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N794" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O794" s="5">
         <v>0</v>
       </c>
       <c r="P794" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q794" s="6">
         <v>96.992668175622086</v>
@@ -43388,13 +43388,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N795" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O795" s="5">
         <v>0</v>
       </c>
       <c r="P795" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q795" s="6">
         <v>174.79142763203379</v>
@@ -43442,13 +43442,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N796" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O796" s="5">
         <v>0</v>
       </c>
       <c r="P796" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q796" s="6">
         <v>135.11949318344401</v>
@@ -43496,13 +43496,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N797" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O797" s="5">
         <v>0</v>
       </c>
       <c r="P797" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q797" s="6">
         <v>74.71932515487569</v>
@@ -43550,13 +43550,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N798" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O798" s="5">
         <v>0</v>
       </c>
       <c r="P798" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q798" s="6">
         <v>125.04183435688761</v>
@@ -43604,13 +43604,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N799" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O799" s="5">
         <v>0</v>
       </c>
       <c r="P799" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q799" s="6">
         <v>209.23141696734811</v>
@@ -43658,13 +43658,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N800" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O800" s="5">
         <v>0</v>
       </c>
       <c r="P800" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q800" s="6">
         <v>183.28128190564499</v>
@@ -43712,13 +43712,13 @@
         <v>5.5399999999999998E-2</v>
       </c>
       <c r="N801" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O801" s="5">
         <v>0</v>
       </c>
       <c r="P801" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q801" s="6">
         <v>70.075881330672104</v>
